--- a/etf_holdings/2026-10-14_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:43</t>
+          <t>2026-10-14 00:27:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:43</t>
+          <t>2026-10-14 00:27:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:43</t>
+          <t>2026-10-14 00:27:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:43</t>
+          <t>2026-10-14 00:27:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:43</t>
+          <t>2026-10-14 00:27:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:43</t>
+          <t>2026-10-14 00:27:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:43</t>
+          <t>2026-10-14 00:27:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:43</t>
+          <t>2026-10-14 00:27:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:43</t>
+          <t>2026-10-14 00:27:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:43</t>
+          <t>2026-10-14 00:27:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:43</t>
+          <t>2026-10-14 00:27:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:43</t>
+          <t>2026-10-14 00:27:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:43</t>
+          <t>2026-10-14 00:27:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:43</t>
+          <t>2026-10-14 00:27:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:43</t>
+          <t>2026-10-14 00:27:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:45</t>
+          <t>2026-10-14 00:27:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:45</t>
+          <t>2026-10-14 00:27:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:45</t>
+          <t>2026-10-14 00:27:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:45</t>
+          <t>2026-10-14 00:27:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:45</t>
+          <t>2026-10-14 00:27:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:45</t>
+          <t>2026-10-14 00:27:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:45</t>
+          <t>2026-10-14 00:27:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:45</t>
+          <t>2026-10-14 00:27:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:45</t>
+          <t>2026-10-14 00:27:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:45</t>
+          <t>2026-10-14 00:27:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:45</t>
+          <t>2026-10-14 00:27:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:45</t>
+          <t>2026-10-14 00:27:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:45</t>
+          <t>2026-10-14 00:27:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:45</t>
+          <t>2026-10-14 00:27:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:45</t>
+          <t>2026-10-14 00:27:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:46</t>
+          <t>2026-10-14 00:27:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:46</t>
+          <t>2026-10-14 00:27:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:46</t>
+          <t>2026-10-14 00:27:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:46</t>
+          <t>2026-10-14 00:27:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:46</t>
+          <t>2026-10-14 00:27:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:46</t>
+          <t>2026-10-14 00:27:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:46</t>
+          <t>2026-10-14 00:27:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:46</t>
+          <t>2026-10-14 00:27:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:46</t>
+          <t>2026-10-14 00:27:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:46</t>
+          <t>2026-10-14 00:27:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:46</t>
+          <t>2026-10-14 00:27:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:46</t>
+          <t>2026-10-14 00:27:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:46</t>
+          <t>2026-10-14 00:27:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:46</t>
+          <t>2026-10-14 00:27:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:46</t>
+          <t>2026-10-14 00:27:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:47</t>
+          <t>2026-10-14 00:27:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:47</t>
+          <t>2026-10-14 00:27:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:47</t>
+          <t>2026-10-14 00:27:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:47</t>
+          <t>2026-10-14 00:27:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:47</t>
+          <t>2026-10-14 00:27:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:47</t>
+          <t>2026-10-14 00:27:32</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-10-14_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:28</t>
+          <t>2026-10-14 01:01:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:28</t>
+          <t>2026-10-14 01:01:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:28</t>
+          <t>2026-10-14 01:01:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:28</t>
+          <t>2026-10-14 01:01:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:28</t>
+          <t>2026-10-14 01:01:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:28</t>
+          <t>2026-10-14 01:01:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:28</t>
+          <t>2026-10-14 01:01:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:28</t>
+          <t>2026-10-14 01:01:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:28</t>
+          <t>2026-10-14 01:01:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:28</t>
+          <t>2026-10-14 01:01:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:28</t>
+          <t>2026-10-14 01:01:52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:28</t>
+          <t>2026-10-14 01:01:52</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:28</t>
+          <t>2026-10-14 01:01:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:28</t>
+          <t>2026-10-14 01:01:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:28</t>
+          <t>2026-10-14 01:01:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:30</t>
+          <t>2026-10-14 01:01:53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:30</t>
+          <t>2026-10-14 01:01:53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:30</t>
+          <t>2026-10-14 01:01:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:30</t>
+          <t>2026-10-14 01:01:53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:30</t>
+          <t>2026-10-14 01:01:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:30</t>
+          <t>2026-10-14 01:01:53</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:30</t>
+          <t>2026-10-14 01:01:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:30</t>
+          <t>2026-10-14 01:01:53</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:30</t>
+          <t>2026-10-14 01:01:53</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:30</t>
+          <t>2026-10-14 01:01:53</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:30</t>
+          <t>2026-10-14 01:01:53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:30</t>
+          <t>2026-10-14 01:01:53</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:30</t>
+          <t>2026-10-14 01:01:53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:30</t>
+          <t>2026-10-14 01:01:53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:30</t>
+          <t>2026-10-14 01:01:53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:31</t>
+          <t>2026-10-14 01:01:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:31</t>
+          <t>2026-10-14 01:01:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:31</t>
+          <t>2026-10-14 01:01:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:31</t>
+          <t>2026-10-14 01:01:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:31</t>
+          <t>2026-10-14 01:01:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:31</t>
+          <t>2026-10-14 01:01:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:31</t>
+          <t>2026-10-14 01:01:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:31</t>
+          <t>2026-10-14 01:01:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:31</t>
+          <t>2026-10-14 01:01:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:31</t>
+          <t>2026-10-14 01:01:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:31</t>
+          <t>2026-10-14 01:01:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:31</t>
+          <t>2026-10-14 01:01:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:31</t>
+          <t>2026-10-14 01:01:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:31</t>
+          <t>2026-10-14 01:01:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:31</t>
+          <t>2026-10-14 01:01:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:32</t>
+          <t>2026-10-14 01:01:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:32</t>
+          <t>2026-10-14 01:01:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:32</t>
+          <t>2026-10-14 01:01:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:32</t>
+          <t>2026-10-14 01:01:55</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:32</t>
+          <t>2026-10-14 01:01:55</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:32</t>
+          <t>2026-10-14 01:01:55</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-10-14_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00400A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:52</t>
+          <t>2026-10-14 21:57:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.97%2490</t>
+          <t>0%2490</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.96%1,094,000</t>
+          <t>8.85%1,094,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.96%</t>
+          <t>8.85%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:52</t>
+          <t>2026-10-14 21:57:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.16%4525</t>
+          <t>-1.1%4475</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4525</v>
+        <v>4475</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.15%413,000</t>
+          <t>6.00%413,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.15%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:52</t>
+          <t>2026-10-14 21:57:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-9.84%5545</t>
+          <t>+9.4%349</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.84%</t>
+          <t>+9.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5545</v>
+        <v>349</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.63%254,000</t>
+          <t>4.72%4,167,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.63%</t>
+          <t>4.72%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>254000</v>
+        <v>4167000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:52</t>
+          <t>2026-10-14 21:57:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+5.28%319</t>
+          <t>-0.45%5520</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+5.28%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>319</v>
+        <v>5520</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.37%4,167,000</t>
+          <t>4.55%254,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.37%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4167000</v>
+        <v>254000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:52</t>
+          <t>2026-10-14 21:57:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-5.98%1180</t>
+          <t>+0.42%1185</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.98%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.15%1,069,000</t>
+          <t>4.11%1,069,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:52</t>
+          <t>2026-10-14 21:57:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-3.1%3280</t>
+          <t>+1.07%3315</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3280</v>
+        <v>3315</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.55%329,000</t>
+          <t>3.54%329,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:52</t>
+          <t>2026-10-14 21:57:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.37%6990</t>
+          <t>+1.14%7070</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6990</v>
+        <v>7070</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:52</t>
+          <t>2026-10-14 21:57:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.1%5940</t>
+          <t>-0.93%5885</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5940</v>
+        <v>5885</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.54%181,000</t>
+          <t>3.46%181,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:52</t>
+          <t>2026-10-14 21:57:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.98%2200</t>
+          <t>+2.27%2250</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.40%470,000</t>
+          <t>3.43%470,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:52</t>
+          <t>2026-10-14 21:57:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-3.52%2195</t>
+          <t>-3.64%2115</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2195</v>
+        <v>2115</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.16%438,197</t>
+          <t>3.01%438,197</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:52</t>
+          <t>2026-10-14 21:57:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-8.97%1015</t>
+          <t>+7.69%1260</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.97%</t>
+          <t>+7.69%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1015</v>
+        <v>1260</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.95%884,000</t>
+          <t>3.00%734,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>884000</v>
+        <v>734000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:52</t>
+          <t>2026-10-14 21:57:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-6.58%1775</t>
+          <t>+0.49%1020</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.58%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1775</v>
+        <v>1020</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.77%475,000</t>
+          <t>2.93%884,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.93%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>475000</v>
+        <v>884000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:52</t>
+          <t>2026-10-14 21:57:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.06%8095</t>
+          <t>+0.56%1785</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8095</v>
+        <v>1785</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.58%97,000</t>
+          <t>2.75%475,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.75%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>97000</v>
+        <v>475000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:52</t>
+          <t>2026-10-14 21:57:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-4.91%10060</t>
+          <t>+1.85%8245</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10060</v>
+        <v>8245</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.58%78,000</t>
+          <t>2.60%97,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.60%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>78000</v>
+        <v>97000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:52</t>
+          <t>2026-10-14 21:57:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-7.74%4055</t>
+          <t>-0.55%10005</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-7.74%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4055</v>
+        <v>10005</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.45%184,000</t>
+          <t>2.53%78,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>184000</v>
+        <v>78000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:53</t>
+          <t>2026-10-14 21:57:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6505台塑化</t>
+          <t>3044健鼎</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+9.68%119</t>
+          <t>+5.42%603</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+9.68%</t>
+          <t>+5.42%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>119</v>
+        <v>603</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.41%6,147,000</t>
+          <t>2.52%1,287,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>6147000</v>
+        <v>1287000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:53</t>
+          <t>2026-10-14 21:57:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>6505台塑化</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-4.48%1600</t>
+          <t>+0.42%119.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-4.48%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1600</v>
+        <v>119.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.08%396,000</t>
+          <t>2.39%6,147,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>396000</v>
+        <v>6147000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:53</t>
+          <t>2026-10-14 21:57:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-5.26%1170</t>
+          <t>-2.84%3940</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1170</v>
+        <v>3940</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.95%507,000</t>
+          <t>2.35%184,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>507000</v>
+        <v>184000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:53</t>
+          <t>2026-10-14 21:57:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3044健鼎</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.21%572</t>
+          <t>+0.35%142</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>572</v>
+        <v>142</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.95%1,034,000</t>
+          <t>1.93%4,192,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1034000</v>
+        <v>4192000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:53</t>
+          <t>2026-10-14 21:57:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.68%7275</t>
+          <t>-1.11%2235</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7275</v>
+        <v>2235</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.70%71,000</t>
+          <t>1.66%228,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>71000</v>
+        <v>228000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:53</t>
+          <t>2026-10-14 21:57:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-4.03%2260</t>
+          <t>+0.31%160.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-4.03%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2260</v>
+        <v>160.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.70%228,000</t>
+          <t>1.62%3,104,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>228000</v>
+        <v>3104000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:53</t>
+          <t>2026-10-14 21:57:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,34 +1785,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.95%160</t>
+          <t>+0.86%17500</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>160</v>
+        <v>17500</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.63%3,104,000</t>
+          <t>1.61%28,400</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>3104000</v>
+        <v>28400</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:53</t>
+          <t>2026-10-14 21:57:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+3.33%264</t>
+          <t>-0.38%263</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+3.33%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.62%1,871,000</t>
+          <t>1.60%1,871,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:53</t>
+          <t>2026-10-14 21:57:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.95%17350</t>
+          <t>-5.43%6880</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>17350</v>
+        <v>6880</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.62%28,400</t>
+          <t>1.59%71,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>28400</v>
+        <v>71000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:53</t>
+          <t>2026-10-14 21:57:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2891中信金</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+2.58%71.6</t>
+          <t>+2.13%216</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>71.59999999999999</v>
+        <v>216</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.54%6,547,000</t>
+          <t>1.55%2,208,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>6547000</v>
+        <v>2208000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:53</t>
+          <t>2026-10-14 21:57:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>2891中信金</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.31%211.5</t>
+          <t>-0.28%71.4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>211.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.54%2,208,000</t>
+          <t>1.52%6,547,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>2208000</v>
+        <v>6547000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:53</t>
+          <t>2026-10-14 21:57:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.4%2810</t>
+          <t>-3.75%1540</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2810</v>
+        <v>1540</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.22%132,000</t>
+          <t>1.48%295,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>132000</v>
+        <v>295000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:53</t>
+          <t>2026-10-14 21:57:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.89%740</t>
+          <t>+4.67%627</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>+4.67%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>740</v>
+        <v>627</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.13%464,000</t>
+          <t>1.44%708,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>464000</v>
+        <v>708000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:53</t>
+          <t>2026-10-14 21:57:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+1.67%305</t>
+          <t>+2.31%2875</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>+2.31%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>305</v>
+        <v>2875</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.00%999,000</t>
+          <t>1.23%132,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>999000</v>
+        <v>132000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:53</t>
+          <t>2026-10-14 21:57:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.32%187</t>
+          <t>+0.95%747</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>187</v>
+        <v>747</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.99%1,614,000</t>
+          <t>1.13%464,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1614000</v>
+        <v>464000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:54</t>
+          <t>2026-10-14 21:57:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-2.75%141.5</t>
+          <t>0%187</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>141.5</v>
+        <v>187</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.98%2,096,000</t>
+          <t>0.98%1,614,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>2096000</v>
+        <v>1614000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:54</t>
+          <t>2026-10-14 21:57:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>6147頎邦</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-5.82%599</t>
+          <t>+4.98%232</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.82%</t>
+          <t>+4.98%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>599</v>
+        <v>232</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.92%469,000</t>
+          <t>0.97%1,293,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>469000</v>
+        <v>1293000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:54</t>
+          <t>2026-10-14 21:57:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,34 +2456,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-3.37%243.5</t>
+          <t>-2.79%296.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-3.37%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>243.5</v>
+        <v>296.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.89%1,107,336</t>
+          <t>0.96%999,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1107336</v>
+        <v>999000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:54</t>
+          <t>2026-10-14 21:57:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.84%240</t>
+          <t>+2.87%250.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+2.87%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>240</v>
+        <v>250.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.76%960,000</t>
+          <t>0.90%1,107,336</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>960000</v>
+        <v>1107336</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:54</t>
+          <t>2026-10-14 21:57:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-9.92%2725</t>
+          <t>+5.69%2880</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-9.92%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2725</v>
+        <v>2880</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.74%82,000</t>
+          <t>0.77%82,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:54</t>
+          <t>2026-10-14 21:57:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7750新代</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-5.22%1815</t>
+          <t>+1.25%243</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5.22%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1815</v>
+        <v>243</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.73%122,000</t>
+          <t>0.76%960,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>122000</v>
+        <v>960000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:54</t>
+          <t>2026-10-14 21:57:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-3.12%264</t>
+          <t>+9.85%290</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.12%</t>
+          <t>+9.85%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.70%804,000</t>
+          <t>0.76%804,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:54</t>
+          <t>2026-10-14 21:57:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3374精材</t>
+          <t>7750新代</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-3.32%465.5</t>
+          <t>+4.13%1890</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-3.32%</t>
+          <t>+4.13%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>465.5</v>
+        <v>1890</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.52%340,000</t>
+          <t>0.75%122,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>340000</v>
+        <v>122000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:54</t>
+          <t>2026-10-14 21:57:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3374精材</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-4.23%2040</t>
+          <t>+7.2%499</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>+7.2%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2040</v>
+        <v>499</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.50%74,000</t>
+          <t>0.55%340,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>74000</v>
+        <v>340000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:54</t>
+          <t>2026-10-14 21:57:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,34 +2883,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2637慧洋-KY</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.98%103</t>
+          <t>+0.49%2050</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>103</v>
+        <v>2050</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.48%1,424,000</t>
+          <t>0.49%74,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1424000</v>
+        <v>74000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:54</t>
+          <t>2026-10-14 21:57:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.06%1860</t>
+          <t>+4.03%1935</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>+4.03%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1860</v>
+        <v>1935</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.47%77,000</t>
+          <t>0.48%77,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:54</t>
+          <t>2026-10-14 21:57:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,34 +3005,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5434崇越</t>
+          <t>2637慧洋-KY</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.34%595</t>
+          <t>+0.49%103.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>595</v>
+        <v>103.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.39%200,000</t>
+          <t>0.48%1,424,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>200000</v>
+        <v>1424000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:54</t>
+          <t>2026-10-14 21:57:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3167大量</t>
+          <t>5434崇越</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-9.95%977</t>
+          <t>+0.17%596</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-9.95%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>977</v>
+        <v>596</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.37%115,000</t>
+          <t>0.39%200,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>115000</v>
+        <v>200000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:54</t>
+          <t>2026-10-14 21:57:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3293鈊象</t>
+          <t>3167大量</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0%797</t>
+          <t>-1.74%960</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.74%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>797</v>
+        <v>960</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.35%133,000</t>
+          <t>0.36%115,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>133000</v>
+        <v>115000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:54</t>
+          <t>2026-10-14 21:57:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.62%167</t>
+          <t>+9.88%183.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.62%</t>
+          <t>+9.88%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>167</v>
+        <v>183.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.33%592,000</t>
+          <t>0.35%592,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:55</t>
+          <t>2026-10-14 21:57:06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6271同欣電</t>
+          <t>3293鈊象</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-3.03%240</t>
+          <t>+1.76%811</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-3.03%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>240</v>
+        <v>811</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.27%340,000</t>
+          <t>0.35%133,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>340000</v>
+        <v>133000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:55</t>
+          <t>2026-10-14 21:57:06</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6121新普</t>
+          <t>6271同欣電</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.96%361</t>
+          <t>+0.83%242</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>361</v>
+        <v>242</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.21%178,000</t>
+          <t>0.27%340,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>178000</v>
+        <v>340000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:55</t>
+          <t>2026-10-14 21:57:06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>6121新普</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-6.47%6070</t>
+          <t>+1.25%365.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-6.47%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>6070</v>
+        <v>365.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.14%7,000</t>
+          <t>0.21%178,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>7000</v>
+        <v>178000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:55</t>
+          <t>2026-10-14 21:57:06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>9939宏全</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+0.8%126</t>
+          <t>-4.78%5780</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>-4.78%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>126</v>
+        <v>5780</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.07%180,000</t>
+          <t>0.13%7,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>180000</v>
+        <v>7000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:55</t>
+          <t>2026-10-14 21:57:06</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,25 +3493,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1476儒鴻</t>
+          <t>9939宏全</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.16%311.5</t>
+          <t>+0.79%127</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>311.5</v>
+        <v>127</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.07%70,000</t>
+          <t>0.07%180,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3520,11 +3520,11 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>70000</v>
+        <v>180000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:55</t>
+          <t>2026-10-14 21:57:06</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3554,41 +3554,102 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>1476儒鴻</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>+0.8%314</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>+0.8%</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>314</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.07%70,000</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>70000</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:57:06</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>1215卜蜂</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-0.47%106</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-0.47%</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>106</v>
-      </c>
-      <c r="I52" t="inlineStr">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>+1.42%107.5</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>+1.42%</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="I53" t="inlineStr">
         <is>
           <t>0.07%200,000</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>0.07%</t>
         </is>
       </c>
-      <c r="K52" t="n">
+      <c r="K53" t="n">
         <v>200000</v>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-14_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:02</t>
+          <t>2026-10-14 22:02:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:02</t>
+          <t>2026-10-14 22:02:35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:02</t>
+          <t>2026-10-14 22:02:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:02</t>
+          <t>2026-10-14 22:02:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:02</t>
+          <t>2026-10-14 22:02:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:02</t>
+          <t>2026-10-14 22:02:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:02</t>
+          <t>2026-10-14 22:02:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:02</t>
+          <t>2026-10-14 22:02:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:02</t>
+          <t>2026-10-14 22:02:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:02</t>
+          <t>2026-10-14 22:02:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:02</t>
+          <t>2026-10-14 22:02:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:02</t>
+          <t>2026-10-14 22:02:35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:02</t>
+          <t>2026-10-14 22:02:35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:02</t>
+          <t>2026-10-14 22:02:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:02</t>
+          <t>2026-10-14 22:02:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:03</t>
+          <t>2026-10-14 22:02:36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:03</t>
+          <t>2026-10-14 22:02:36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:03</t>
+          <t>2026-10-14 22:02:36</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:03</t>
+          <t>2026-10-14 22:02:36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:03</t>
+          <t>2026-10-14 22:02:36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:03</t>
+          <t>2026-10-14 22:02:36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:03</t>
+          <t>2026-10-14 22:02:36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:03</t>
+          <t>2026-10-14 22:02:36</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:03</t>
+          <t>2026-10-14 22:02:36</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:03</t>
+          <t>2026-10-14 22:02:36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:03</t>
+          <t>2026-10-14 22:02:36</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:03</t>
+          <t>2026-10-14 22:02:36</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:03</t>
+          <t>2026-10-14 22:02:36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:03</t>
+          <t>2026-10-14 22:02:36</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:03</t>
+          <t>2026-10-14 22:02:36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:05</t>
+          <t>2026-10-14 22:02:38</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:05</t>
+          <t>2026-10-14 22:02:38</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:05</t>
+          <t>2026-10-14 22:02:38</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:05</t>
+          <t>2026-10-14 22:02:38</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:05</t>
+          <t>2026-10-14 22:02:38</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:05</t>
+          <t>2026-10-14 22:02:38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:05</t>
+          <t>2026-10-14 22:02:38</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:05</t>
+          <t>2026-10-14 22:02:38</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:05</t>
+          <t>2026-10-14 22:02:38</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:05</t>
+          <t>2026-10-14 22:02:38</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:05</t>
+          <t>2026-10-14 22:02:38</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:05</t>
+          <t>2026-10-14 22:02:38</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:05</t>
+          <t>2026-10-14 22:02:38</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:05</t>
+          <t>2026-10-14 22:02:38</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:05</t>
+          <t>2026-10-14 22:02:38</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:06</t>
+          <t>2026-10-14 22:02:39</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:06</t>
+          <t>2026-10-14 22:02:39</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:06</t>
+          <t>2026-10-14 22:02:39</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:06</t>
+          <t>2026-10-14 22:02:39</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:06</t>
+          <t>2026-10-14 22:02:39</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:06</t>
+          <t>2026-10-14 22:02:39</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-14 21:57:06</t>
+          <t>2026-10-14 22:02:39</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">

--- a/etf_holdings/2026-10-14_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:35</t>
+          <t>2026-10-14 22:33:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:35</t>
+          <t>2026-10-14 22:33:01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:35</t>
+          <t>2026-10-14 22:33:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:35</t>
+          <t>2026-10-14 22:33:01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:35</t>
+          <t>2026-10-14 22:33:01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:35</t>
+          <t>2026-10-14 22:33:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:35</t>
+          <t>2026-10-14 22:33:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:35</t>
+          <t>2026-10-14 22:33:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:35</t>
+          <t>2026-10-14 22:33:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:35</t>
+          <t>2026-10-14 22:33:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:35</t>
+          <t>2026-10-14 22:33:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:35</t>
+          <t>2026-10-14 22:33:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:35</t>
+          <t>2026-10-14 22:33:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:35</t>
+          <t>2026-10-14 22:33:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:35</t>
+          <t>2026-10-14 22:33:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:36</t>
+          <t>2026-10-14 22:33:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:36</t>
+          <t>2026-10-14 22:33:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:36</t>
+          <t>2026-10-14 22:33:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:36</t>
+          <t>2026-10-14 22:33:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:36</t>
+          <t>2026-10-14 22:33:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:36</t>
+          <t>2026-10-14 22:33:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:36</t>
+          <t>2026-10-14 22:33:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:36</t>
+          <t>2026-10-14 22:33:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:36</t>
+          <t>2026-10-14 22:33:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:36</t>
+          <t>2026-10-14 22:33:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:36</t>
+          <t>2026-10-14 22:33:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:36</t>
+          <t>2026-10-14 22:33:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:36</t>
+          <t>2026-10-14 22:33:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:36</t>
+          <t>2026-10-14 22:33:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:36</t>
+          <t>2026-10-14 22:33:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:38</t>
+          <t>2026-10-14 22:33:04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:38</t>
+          <t>2026-10-14 22:33:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:38</t>
+          <t>2026-10-14 22:33:04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:38</t>
+          <t>2026-10-14 22:33:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:38</t>
+          <t>2026-10-14 22:33:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:38</t>
+          <t>2026-10-14 22:33:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:38</t>
+          <t>2026-10-14 22:33:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:38</t>
+          <t>2026-10-14 22:33:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:38</t>
+          <t>2026-10-14 22:33:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:38</t>
+          <t>2026-10-14 22:33:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:38</t>
+          <t>2026-10-14 22:33:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:38</t>
+          <t>2026-10-14 22:33:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:38</t>
+          <t>2026-10-14 22:33:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:38</t>
+          <t>2026-10-14 22:33:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:38</t>
+          <t>2026-10-14 22:33:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:39</t>
+          <t>2026-10-14 22:33:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:39</t>
+          <t>2026-10-14 22:33:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:39</t>
+          <t>2026-10-14 22:33:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:39</t>
+          <t>2026-10-14 22:33:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:39</t>
+          <t>2026-10-14 22:33:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:39</t>
+          <t>2026-10-14 22:33:05</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:39</t>
+          <t>2026-10-14 22:33:05</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
